--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -408,33 +408,55 @@
     <t>Appointment.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedioNotificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MedioNotificacion}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Contactado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Contactado}
+</t>
+  </si>
+  <si>
+    <t>Appointment.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Appointment.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -442,6 +464,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -498,17 +523,13 @@
     <t>Appointment.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1570,11 +1591,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.66796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.35546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2537,11 +2558,11 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -2556,17 +2577,15 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>131</v>
-      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
         <v>73</v>
@@ -2603,16 +2622,14 @@
         <v>73</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AB9" s="2"/>
       <c r="AC9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AE9" t="s" s="2">
         <v>132</v>
@@ -2633,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2645,45 +2662,43 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
       <c r="O10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2731,7 +2746,7 @@
         <v>73</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>74</v>
@@ -2740,7 +2755,7 @@
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>133</v>
@@ -2749,7 +2764,7 @@
         <v>73</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2763,9 +2778,11 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="C11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2783,16 +2800,16 @@
         <v>73</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -2843,7 +2860,7 @@
         <v>73</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>74</v>
@@ -2852,62 +2869,66 @@
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O12" t="s" s="2">
         <v>73</v>
       </c>
@@ -2955,25 +2976,25 @@
         <v>73</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2985,42 +3006,40 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
         <v>73</v>
@@ -3057,19 +3076,19 @@
         <v>73</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="AC13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>74</v>
@@ -3081,27 +3100,27 @@
         <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3118,26 +3137,22 @@
         <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
         <v>73</v>
       </c>
@@ -3161,13 +3176,13 @@
         <v>73</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>73</v>
@@ -3185,7 +3200,7 @@
         <v>73</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>74</v>
@@ -3197,13 +3212,13 @@
         <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3212,23 +3227,23 @@
         <v>73</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>125</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>73</v>
@@ -3237,23 +3252,21 @@
         <v>73</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
         <v>73</v>
       </c>
@@ -3277,49 +3290,49 @@
         <v>73</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3328,12 +3341,12 @@
         <v>73</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3341,34 +3354,34 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>73</v>
@@ -3381,7 +3394,7 @@
         <v>73</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>73</v>
@@ -3393,13 +3406,13 @@
         <v>73</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>73</v>
@@ -3417,7 +3430,7 @@
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>74</v>
@@ -3435,7 +3448,7 @@
         <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>73</v>
@@ -3444,12 +3457,12 @@
         <v>73</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3457,13 +3470,13 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -3472,18 +3485,20 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O17" t="s" s="2">
         <v>73</v>
       </c>
@@ -3495,7 +3510,7 @@
         <v>73</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>73</v>
@@ -3507,13 +3522,13 @@
         <v>73</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -3531,7 +3546,7 @@
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>74</v>
@@ -3549,7 +3564,7 @@
         <v>73</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3558,12 +3573,12 @@
         <v>73</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3586,16 +3601,20 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="O18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3607,7 +3626,7 @@
         <v>73</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>73</v>
@@ -3643,7 +3662,7 @@
         <v>73</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>74</v>
@@ -3661,7 +3680,7 @@
         <v>73</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
@@ -3670,12 +3689,12 @@
         <v>73</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3683,13 +3702,13 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -3698,16 +3717,16 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
@@ -3721,7 +3740,7 @@
         <v>73</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>73</v>
@@ -3757,7 +3776,7 @@
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>74</v>
@@ -3775,7 +3794,7 @@
         <v>73</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3784,12 +3803,12 @@
         <v>73</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3797,32 +3816,30 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
         <v>73</v>
@@ -3832,7 +3849,7 @@
         <v>73</v>
       </c>
       <c r="R20" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>73</v>
@@ -3847,13 +3864,13 @@
         <v>73</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>219</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -3871,10 +3888,10 @@
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -3886,24 +3903,24 @@
         <v>94</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>73</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3926,15 +3943,17 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>73</v>
@@ -3959,11 +3978,13 @@
         <v>73</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="X21" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Y21" t="s" s="2">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>73</v>
@@ -3981,7 +4002,7 @@
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>74</v>
@@ -3999,7 +4020,7 @@
         <v>73</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -4008,12 +4029,12 @@
         <v>73</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>73</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4021,30 +4042,32 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>73</v>
@@ -4054,7 +4077,7 @@
         <v>73</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>73</v>
@@ -4069,11 +4092,13 @@
         <v>73</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="X22" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="Y22" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -4091,13 +4116,13 @@
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>73</v>
@@ -4106,24 +4131,24 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>73</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>73</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4134,7 +4159,7 @@
         <v>74</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>73</v>
@@ -4146,17 +4171,15 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>73</v>
@@ -4181,11 +4204,11 @@
         <v>73</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="X23" s="2"/>
       <c r="Y23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>73</v>
@@ -4203,13 +4226,13 @@
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>73</v>
@@ -4218,10 +4241,10 @@
         <v>94</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -4235,7 +4258,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4258,13 +4281,13 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4291,11 +4314,11 @@
         <v>73</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="X24" s="2"/>
       <c r="Y24" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -4313,7 +4336,7 @@
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>74</v>
@@ -4331,13 +4354,13 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>73</v>
@@ -4345,7 +4368,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4356,7 +4379,7 @@
         <v>74</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>73</v>
@@ -4368,15 +4391,17 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>73</v>
@@ -4401,11 +4426,11 @@
         <v>73</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="X25" s="2"/>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -4423,13 +4448,13 @@
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>73</v>
@@ -4438,24 +4463,24 @@
         <v>94</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>73</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>254</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4478,13 +4503,13 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4513,11 +4538,9 @@
       <c r="W26" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="X26" t="s" s="2">
-        <v>258</v>
-      </c>
+      <c r="X26" s="2"/>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -4535,7 +4558,7 @@
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4550,24 +4573,24 @@
         <v>94</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>260</v>
+        <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>73</v>
+        <v>253</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4578,7 +4601,7 @@
         <v>74</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>73</v>
@@ -4587,16 +4610,16 @@
         <v>73</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4623,13 +4646,11 @@
         <v>73</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="X27" s="2"/>
       <c r="Y27" t="s" s="2">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -4647,13 +4668,13 @@
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>73</v>
@@ -4662,24 +4683,24 @@
         <v>94</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>73</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4690,7 +4711,7 @@
         <v>74</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>73</v>
@@ -4699,20 +4720,18 @@
         <v>73</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>270</v>
+        <v>177</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>73</v>
@@ -4737,13 +4756,13 @@
         <v>73</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>73</v>
+        <v>264</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -4761,13 +4780,13 @@
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>73</v>
@@ -4776,24 +4795,24 @@
         <v>94</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4804,7 +4823,7 @@
         <v>74</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>73</v>
@@ -4816,13 +4835,13 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>149</v>
+        <v>270</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -4873,13 +4892,13 @@
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>73</v>
@@ -4888,24 +4907,24 @@
         <v>94</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
+        <v>273</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>73</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4916,7 +4935,7 @@
         <v>74</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>73</v>
@@ -4928,15 +4947,17 @@
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="M30" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>73</v>
@@ -4985,13 +5006,13 @@
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>73</v>
@@ -5000,24 +5021,24 @@
         <v>94</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>73</v>
+        <v>283</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5025,28 +5046,28 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>293</v>
+        <v>156</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5097,7 +5118,7 @@
         <v>73</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>74</v>
@@ -5112,24 +5133,24 @@
         <v>94</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>73</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5140,7 +5161,7 @@
         <v>74</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>73</v>
@@ -5149,16 +5170,16 @@
         <v>73</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5209,13 +5230,13 @@
         <v>73</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>73</v>
@@ -5224,24 +5245,24 @@
         <v>94</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>307</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5255,22 +5276,22 @@
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5321,7 +5342,7 @@
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5336,24 +5357,24 @@
         <v>94</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>73</v>
+        <v>305</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>73</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5364,7 +5385,7 @@
         <v>74</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>73</v>
@@ -5373,16 +5394,16 @@
         <v>73</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -5433,13 +5454,13 @@
         <v>73</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>73</v>
@@ -5448,24 +5469,24 @@
         <v>94</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>73</v>
+        <v>302</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>73</v>
+        <v>311</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>73</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5488,17 +5509,15 @@
         <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>73</v>
@@ -5547,7 +5566,7 @@
         <v>73</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>74</v>
@@ -5562,13 +5581,13 @@
         <v>94</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>73</v>
@@ -5579,7 +5598,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5590,7 +5609,7 @@
         <v>74</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>73</v>
@@ -5602,17 +5621,15 @@
         <v>73</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>149</v>
+        <v>321</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>73</v>
@@ -5661,13 +5678,13 @@
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>73</v>
@@ -5676,24 +5693,24 @@
         <v>94</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>331</v>
+        <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>333</v>
+        <v>73</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5716,15 +5733,17 @@
         <v>73</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>149</v>
+        <v>326</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>73</v>
@@ -5773,7 +5792,7 @@
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -5788,35 +5807,35 @@
         <v>94</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AM37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>339</v>
+        <v>73</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>73</v>
@@ -5828,15 +5847,17 @@
         <v>73</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>340</v>
+        <v>156</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M38" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
         <v>73</v>
@@ -5885,13 +5906,13 @@
         <v>73</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>73</v>
@@ -5900,24 +5921,24 @@
         <v>94</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>73</v>
+        <v>339</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>73</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5925,11 +5946,11 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="F39" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="G39" t="s" s="2">
         <v>73</v>
       </c>
@@ -5940,13 +5961,13 @@
         <v>73</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>346</v>
+        <v>156</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -5997,53 +6018,53 @@
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AH39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>349</v>
+        <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>350</v>
+        <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>353</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -6052,13 +6073,13 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>149</v>
+        <v>346</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>150</v>
+        <v>347</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>151</v>
+        <v>348</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6109,25 +6130,25 @@
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>152</v>
+        <v>344</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>73</v>
+        <v>349</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>153</v>
+        <v>350</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6141,15 +6162,15 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>75</v>
@@ -6164,17 +6185,15 @@
         <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>128</v>
+        <v>352</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>129</v>
+        <v>353</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
         <v>73</v>
@@ -6223,10 +6242,10 @@
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>159</v>
+        <v>351</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6235,63 +6254,59 @@
         <v>73</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>133</v>
+        <v>355</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>153</v>
+        <v>357</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>73</v>
+        <v>358</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>73</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>357</v>
+        <v>73</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>358</v>
+        <v>157</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>73</v>
       </c>
@@ -6339,25 +6354,25 @@
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>360</v>
+        <v>159</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6375,7 +6390,7 @@
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6391,19 +6406,19 @@
         <v>73</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>362</v>
+        <v>162</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
+        <v>143</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -6429,13 +6444,13 @@
         <v>73</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>365</v>
+        <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>73</v>
@@ -6453,7 +6468,7 @@
         <v>73</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>74</v>
@@ -6465,59 +6480,63 @@
         <v>73</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>367</v>
+        <v>160</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>368</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>370</v>
+        <v>127</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O44" t="s" s="2">
         <v>73</v>
       </c>
@@ -6565,39 +6584,39 @@
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>373</v>
+        <v>125</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>374</v>
+        <v>73</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>375</v>
+        <v>73</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>376</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6608,7 +6627,7 @@
         <v>74</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>73</v>
@@ -6620,15 +6639,17 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M45" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>73</v>
@@ -6653,13 +6674,13 @@
         <v>73</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>73</v>
@@ -6677,13 +6698,13 @@
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>73</v>
@@ -6695,21 +6716,21 @@
         <v>73</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>383</v>
+        <v>160</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>73</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6717,7 +6738,7 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>82</v>
@@ -6732,13 +6753,13 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>102</v>
+        <v>376</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6765,13 +6786,13 @@
         <v>73</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>387</v>
+        <v>73</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>388</v>
+        <v>73</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>73</v>
@@ -6789,10 +6810,10 @@
         <v>73</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -6807,21 +6828,21 @@
         <v>73</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>73</v>
+        <v>381</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -6841,16 +6862,16 @@
         <v>73</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6877,13 +6898,13 @@
         <v>73</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>73</v>
+        <v>386</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>73</v>
+        <v>387</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>73</v>
@@ -6901,7 +6922,7 @@
         <v>73</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
@@ -6919,10 +6940,10 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>153</v>
+        <v>388</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>73</v>
+        <v>389</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>73</v>
@@ -6933,7 +6954,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -6941,10 +6962,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>73</v>
@@ -6953,20 +6974,18 @@
         <v>73</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>73</v>
@@ -6991,13 +7010,13 @@
         <v>73</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>73</v>
+        <v>393</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>73</v>
+        <v>394</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>73</v>
@@ -7015,13 +7034,13 @@
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>73</v>
@@ -7030,23 +7049,249 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="L49" t="s" s="2">
         <v>400</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN48">
+  <autoFilter ref="A1:AN50">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7056,7 +7301,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-20T17:48:12+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -432,22 +432,28 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>MedioNotificacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MedioNotificacion}
+    <t>ExtBoolMedioNotificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolMedioNotificacion}
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExtBool Medio Notificacion </t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Contactado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Contactado}
+    <t>ContactadoLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ContactadoLE}
 </t>
+  </si>
+  <si>
+    <t>Contacto del paciente</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>
@@ -822,6 +828,185 @@
   </si>
   <si>
     <t>ARQ-7</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.id</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.extension</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.id</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.extension</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Appointment.appointmentType.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Appointment.reasonCode</t>
@@ -1190,7 +1375,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device|HealthcareService|Location)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
 </t>
   </si>
   <si>
@@ -1591,11 +1776,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.66796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="17.35546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.0078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2562,7 +2747,7 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -2692,10 +2877,10 @@
         <v>135</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -2755,7 +2940,7 @@
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>133</v>
@@ -2781,14 +2966,14 @@
         <v>126</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>82</v>
@@ -2803,13 +2988,13 @@
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -2869,7 +3054,7 @@
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>133</v>
@@ -2892,11 +3077,11 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -2918,16 +3103,16 @@
         <v>127</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O12" t="s" s="2">
         <v>73</v>
@@ -2976,7 +3161,7 @@
         <v>73</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>74</v>
@@ -3008,7 +3193,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -3031,13 +3216,13 @@
         <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -3088,7 +3273,7 @@
         <v>73</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>74</v>
@@ -3103,24 +3288,24 @@
         <v>94</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3143,13 +3328,13 @@
         <v>73</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -3200,7 +3385,7 @@
         <v>73</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>74</v>
@@ -3218,7 +3403,7 @@
         <v>73</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3232,11 +3417,11 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3258,13 +3443,13 @@
         <v>127</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
@@ -3305,7 +3490,7 @@
         <v>130</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>73</v>
@@ -3314,7 +3499,7 @@
         <v>131</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>74</v>
@@ -3332,7 +3517,7 @@
         <v>73</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3346,7 +3531,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3372,16 +3557,16 @@
         <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>73</v>
@@ -3406,13 +3591,13 @@
         <v>73</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>73</v>
@@ -3430,7 +3615,7 @@
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>74</v>
@@ -3448,7 +3633,7 @@
         <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>73</v>
@@ -3462,7 +3647,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3485,19 +3670,19 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>73</v>
@@ -3522,13 +3707,13 @@
         <v>73</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -3546,7 +3731,7 @@
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>74</v>
@@ -3564,7 +3749,7 @@
         <v>73</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3573,12 +3758,12 @@
         <v>73</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3604,16 +3789,16 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>73</v>
@@ -3626,7 +3811,7 @@
         <v>73</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>73</v>
@@ -3662,7 +3847,7 @@
         <v>73</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>74</v>
@@ -3680,7 +3865,7 @@
         <v>73</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
@@ -3689,12 +3874,12 @@
         <v>73</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3717,16 +3902,16 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
@@ -3740,7 +3925,7 @@
         <v>73</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>73</v>
@@ -3776,7 +3961,7 @@
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>74</v>
@@ -3794,7 +3979,7 @@
         <v>73</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3803,12 +3988,12 @@
         <v>73</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3831,13 +4016,13 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3888,7 +4073,7 @@
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>74</v>
@@ -3906,7 +4091,7 @@
         <v>73</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>73</v>
@@ -3915,12 +4100,12 @@
         <v>73</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3943,16 +4128,16 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4002,7 +4187,7 @@
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>74</v>
@@ -4020,7 +4205,7 @@
         <v>73</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -4029,12 +4214,12 @@
         <v>73</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4060,13 +4245,13 @@
         <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
@@ -4077,7 +4262,7 @@
         <v>73</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>73</v>
@@ -4092,13 +4277,13 @@
         <v>73</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -4116,7 +4301,7 @@
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>82</v>
@@ -4131,24 +4316,24 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4171,13 +4356,13 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4204,11 +4389,11 @@
         <v>73</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="X23" s="2"/>
       <c r="Y23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>73</v>
@@ -4226,7 +4411,7 @@
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
@@ -4244,7 +4429,7 @@
         <v>73</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -4258,7 +4443,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4281,13 +4466,13 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4314,11 +4499,11 @@
         <v>73</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="X24" s="2"/>
       <c r="Y24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -4336,7 +4521,7 @@
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>74</v>
@@ -4354,10 +4539,10 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>73</v>
@@ -4368,7 +4553,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4391,16 +4576,16 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -4426,11 +4611,11 @@
         <v>73</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="X25" s="2"/>
       <c r="Y25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -4448,7 +4633,7 @@
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>74</v>
@@ -4463,10 +4648,10 @@
         <v>94</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4480,7 +4665,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4503,13 +4688,13 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4540,7 +4725,7 @@
       </c>
       <c r="X26" s="2"/>
       <c r="Y26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -4558,7 +4743,7 @@
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4576,21 +4761,21 @@
         <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4604,7 +4789,7 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -4613,13 +4798,13 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4650,7 +4835,7 @@
       </c>
       <c r="X27" s="2"/>
       <c r="Y27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -4668,7 +4853,7 @@
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>74</v>
@@ -4686,21 +4871,21 @@
         <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4711,7 +4896,7 @@
         <v>74</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>73</v>
@@ -4720,16 +4905,16 @@
         <v>73</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4756,13 +4941,13 @@
         <v>73</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>264</v>
+        <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -4780,25 +4965,25 @@
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>261</v>
+        <v>161</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>162</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4807,16 +4992,16 @@
         <v>73</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4835,15 +5020,17 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>270</v>
+        <v>127</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M29" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
         <v>73</v>
@@ -4880,19 +5067,19 @@
         <v>73</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AC29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>74</v>
@@ -4904,13 +5091,13 @@
         <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>274</v>
+        <v>162</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4922,9 +5109,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4932,33 +5119,35 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>73</v>
       </c>
@@ -5006,13 +5195,13 @@
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>73</v>
@@ -5021,24 +5210,24 @@
         <v>94</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>280</v>
+        <v>73</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>73</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>253</v>
+        <v>73</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5061,13 +5250,13 @@
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>285</v>
+        <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>160</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5118,7 +5307,7 @@
         <v>73</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>74</v>
@@ -5130,31 +5319,31 @@
         <v>73</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>287</v>
+        <v>162</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>288</v>
+        <v>73</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>289</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5173,15 +5362,17 @@
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>291</v>
+        <v>127</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>292</v>
+        <v>164</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M32" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>73</v>
@@ -5218,19 +5409,19 @@
         <v>73</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>290</v>
+        <v>167</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>74</v>
@@ -5242,19 +5433,19 @@
         <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>294</v>
+        <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>295</v>
+        <v>162</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>73</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>73</v>
@@ -5262,7 +5453,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5270,7 +5461,7 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>82</v>
@@ -5285,16 +5476,20 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>299</v>
+        <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="O33" t="s" s="2">
         <v>73</v>
       </c>
@@ -5342,7 +5537,7 @@
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5357,24 +5552,24 @@
         <v>94</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>304</v>
+        <v>73</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>305</v>
+        <v>73</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>306</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5397,15 +5592,17 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>299</v>
+        <v>158</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M34" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>73</v>
@@ -5454,7 +5651,7 @@
         <v>73</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>74</v>
@@ -5469,24 +5666,24 @@
         <v>94</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>311</v>
+        <v>73</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>312</v>
+        <v>73</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5494,31 +5691,33 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>315</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O35" t="s" s="2">
         <v>73</v>
       </c>
@@ -5566,7 +5765,7 @@
         <v>73</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>74</v>
@@ -5581,24 +5780,24 @@
         <v>94</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>319</v>
+        <v>73</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>73</v>
+        <v>297</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5609,28 +5808,30 @@
         <v>74</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O36" t="s" s="2">
         <v>73</v>
       </c>
@@ -5678,13 +5879,13 @@
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>73</v>
@@ -5696,7 +5897,7 @@
         <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5705,12 +5906,12 @@
         <v>73</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>73</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5730,21 +5931,23 @@
         <v>73</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O37" t="s" s="2">
         <v>73</v>
       </c>
@@ -5792,7 +5995,7 @@
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -5807,24 +6010,24 @@
         <v>94</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>330</v>
+        <v>73</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>332</v>
+        <v>73</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>73</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -5838,27 +6041,29 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O38" t="s" s="2">
         <v>73</v>
       </c>
@@ -5906,7 +6111,7 @@
         <v>73</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
@@ -5921,24 +6126,24 @@
         <v>94</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>337</v>
+        <v>73</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>339</v>
+        <v>73</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>289</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5949,7 +6154,7 @@
         <v>74</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>73</v>
@@ -5958,16 +6163,16 @@
         <v>73</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -5994,13 +6199,13 @@
         <v>73</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>325</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -6018,13 +6223,13 @@
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>73</v>
@@ -6033,38 +6238,38 @@
         <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>343</v>
+        <v>73</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>289</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>345</v>
+        <v>73</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -6073,13 +6278,13 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6130,7 +6335,7 @@
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
@@ -6145,10 +6350,10 @@
         <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6162,7 +6367,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6170,11 +6375,11 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="F41" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="G41" t="s" s="2">
         <v>73</v>
       </c>
@@ -6185,15 +6390,17 @@
         <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M41" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
         <v>73</v>
@@ -6242,39 +6449,39 @@
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AH41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>355</v>
+        <v>94</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>359</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6297,13 +6504,13 @@
         <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>346</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>347</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -6354,7 +6561,7 @@
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>159</v>
+        <v>345</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
@@ -6366,31 +6573,31 @@
         <v>73</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>73</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>73</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6409,17 +6616,15 @@
         <v>73</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>127</v>
+        <v>352</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>73</v>
@@ -6468,7 +6673,7 @@
         <v>73</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>165</v>
+        <v>351</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>74</v>
@@ -6480,63 +6685,59 @@
         <v>73</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>73</v>
+        <v>355</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>160</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>73</v>
+        <v>357</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>73</v>
+        <v>358</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>363</v>
+        <v>73</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>127</v>
+        <v>360</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>73</v>
       </c>
@@ -6584,39 +6785,39 @@
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AF44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>73</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6627,7 +6828,7 @@
         <v>74</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>73</v>
@@ -6639,17 +6840,15 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>177</v>
+        <v>360</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M45" t="s" s="2">
         <v>370</v>
       </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>73</v>
@@ -6674,13 +6873,13 @@
         <v>73</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>371</v>
+        <v>73</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>372</v>
+        <v>73</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>73</v>
@@ -6698,13 +6897,13 @@
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>73</v>
@@ -6713,16 +6912,16 @@
         <v>94</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>374</v>
@@ -6750,7 +6949,7 @@
         <v>73</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>376</v>
@@ -6825,7 +7024,7 @@
         <v>94</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>379</v>
@@ -6834,15 +7033,15 @@
         <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>381</v>
+        <v>73</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>382</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -6853,7 +7052,7 @@
         <v>74</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>73</v>
@@ -6862,16 +7061,16 @@
         <v>73</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>102</v>
+        <v>382</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6898,13 +7097,13 @@
         <v>73</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>386</v>
+        <v>73</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>387</v>
+        <v>73</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>73</v>
@@ -6922,13 +7121,13 @@
         <v>73</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>73</v>
@@ -6940,10 +7139,10 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>389</v>
+        <v>73</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>73</v>
@@ -6952,9 +7151,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -6962,30 +7161,32 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>102</v>
+        <v>387</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M48" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>73</v>
@@ -7010,13 +7211,13 @@
         <v>73</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>393</v>
+        <v>73</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>394</v>
+        <v>73</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>73</v>
@@ -7034,10 +7235,10 @@
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7049,24 +7250,24 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>73</v>
+        <v>391</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>397</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7089,15 +7290,17 @@
         <v>73</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M49" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>73</v>
@@ -7146,7 +7349,7 @@
         <v>73</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>74</v>
@@ -7161,19 +7364,19 @@
         <v>94</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>73</v>
+        <v>398</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>160</v>
+        <v>399</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>73</v>
+        <v>400</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>73</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7189,7 +7392,7 @@
         <v>74</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>73</v>
@@ -7201,7 +7404,7 @@
         <v>73</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>402</v>
@@ -7209,9 +7412,7 @@
       <c r="L50" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
         <v>73</v>
@@ -7266,7 +7467,7 @@
         <v>74</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>73</v>
@@ -7275,23 +7476,1265 @@
         <v>94</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="B51" s="2"/>
+      <c r="C51" t="s" s="2">
         <v>406</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P53" s="2"/>
+      <c r="Q53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P56" s="2"/>
+      <c r="Q56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P58" s="2"/>
+      <c r="Q58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P60" s="2"/>
+      <c r="Q60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN50">
+  <autoFilter ref="A1:AN61">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7301,7 +8744,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -432,14 +432,11 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ExtBoolMedioNotificacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolMedioNotificacion}
+    <t>MedioNotificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MedioNotificacion}
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExtBool Medio Notificacion </t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -449,11 +446,11 @@
     <t>ContactadoLE</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ContactadoLE}
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Contactado}
 </t>
   </si>
   <si>
-    <t>Contacto del paciente</t>
+    <t>Contactado</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>
@@ -1780,7 +1777,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.0078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.35546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2877,10 +2874,10 @@
         <v>135</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -2940,7 +2937,7 @@
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>133</v>
@@ -2966,7 +2963,7 @@
         <v>126</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>73</v>
@@ -2988,13 +2985,13 @@
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="K11" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -3054,7 +3051,7 @@
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>133</v>
@@ -3077,11 +3074,11 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -3103,16 +3100,16 @@
         <v>127</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O12" t="s" s="2">
         <v>73</v>
@@ -3161,7 +3158,7 @@
         <v>73</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>74</v>
@@ -3193,7 +3190,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -3216,13 +3213,13 @@
         <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="K13" t="s" s="2">
+      <c r="L13" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -3273,7 +3270,7 @@
         <v>73</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>74</v>
@@ -3288,24 +3285,24 @@
         <v>94</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3328,13 +3325,13 @@
         <v>73</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -3385,7 +3382,7 @@
         <v>73</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>74</v>
@@ -3403,7 +3400,7 @@
         <v>73</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3417,11 +3414,11 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3443,13 +3440,13 @@
         <v>127</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
@@ -3490,7 +3487,7 @@
         <v>130</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>73</v>
@@ -3499,7 +3496,7 @@
         <v>131</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>74</v>
@@ -3517,7 +3514,7 @@
         <v>73</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3531,7 +3528,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3557,16 +3554,16 @@
         <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>73</v>
@@ -3591,31 +3588,31 @@
         <v>73</v>
       </c>
       <c r="W16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="X16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="X16" t="s" s="2">
+      <c r="Y16" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>74</v>
@@ -3633,7 +3630,7 @@
         <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>73</v>
@@ -3647,7 +3644,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3670,19 +3667,19 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>73</v>
@@ -3707,31 +3704,31 @@
         <v>73</v>
       </c>
       <c r="W17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>74</v>
@@ -3749,7 +3746,7 @@
         <v>73</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3758,12 +3755,12 @@
         <v>73</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3789,16 +3786,16 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>73</v>
@@ -3811,43 +3808,43 @@
         <v>73</v>
       </c>
       <c r="S18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>74</v>
@@ -3865,21 +3862,21 @@
         <v>73</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3902,16 +3899,16 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
@@ -3925,43 +3922,43 @@
         <v>73</v>
       </c>
       <c r="S19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>74</v>
@@ -3979,21 +3976,21 @@
         <v>73</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -4016,13 +4013,13 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="K20" t="s" s="2">
+      <c r="L20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -4073,7 +4070,7 @@
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>74</v>
@@ -4091,21 +4088,21 @@
         <v>73</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -4128,16 +4125,16 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="K21" t="s" s="2">
+      <c r="L21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4187,7 +4184,7 @@
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>74</v>
@@ -4205,21 +4202,21 @@
         <v>73</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4245,13 +4242,13 @@
         <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
@@ -4262,29 +4259,29 @@
         <v>73</v>
       </c>
       <c r="R22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="X22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="S22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="X22" t="s" s="2">
+      <c r="Y22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Y22" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
       </c>
@@ -4301,7 +4298,7 @@
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>82</v>
@@ -4316,24 +4313,24 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4356,13 +4353,13 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4389,11 +4386,11 @@
         <v>73</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X23" s="2"/>
       <c r="Y23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>73</v>
@@ -4411,7 +4408,7 @@
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
@@ -4429,7 +4426,7 @@
         <v>73</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4466,13 +4463,13 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4499,11 +4496,11 @@
         <v>73</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X24" s="2"/>
       <c r="Y24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -4521,7 +4518,7 @@
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>74</v>
@@ -4539,10 +4536,10 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>73</v>
@@ -4553,7 +4550,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4576,16 +4573,16 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -4611,11 +4608,11 @@
         <v>73</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X25" s="2"/>
       <c r="Y25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -4633,7 +4630,7 @@
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>74</v>
@@ -4648,10 +4645,10 @@
         <v>94</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4665,7 +4662,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4688,13 +4685,13 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4725,7 +4722,7 @@
       </c>
       <c r="X26" s="2"/>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -4743,7 +4740,7 @@
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4761,13 +4758,13 @@
         <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>73</v>
@@ -4775,7 +4772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4798,13 +4795,13 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4835,7 +4832,7 @@
       </c>
       <c r="X27" s="2"/>
       <c r="Y27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -4853,7 +4850,7 @@
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>74</v>
@@ -4871,21 +4868,21 @@
         <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4908,13 +4905,13 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K28" t="s" s="2">
+      <c r="L28" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4965,7 +4962,7 @@
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>74</v>
@@ -4983,7 +4980,7 @@
         <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4997,11 +4994,11 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5023,13 +5020,13 @@
         <v>127</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
@@ -5070,7 +5067,7 @@
         <v>130</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC29" t="s" s="2">
         <v>73</v>
@@ -5079,7 +5076,7 @@
         <v>131</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>74</v>
@@ -5097,7 +5094,7 @@
         <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -5111,7 +5108,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5134,19 +5131,19 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="K30" t="s" s="2">
+      <c r="L30" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>73</v>
@@ -5195,7 +5192,7 @@
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
@@ -5213,21 +5210,21 @@
         <v>73</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5250,13 +5247,13 @@
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K31" t="s" s="2">
+      <c r="L31" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5307,7 +5304,7 @@
         <v>73</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>74</v>
@@ -5325,7 +5322,7 @@
         <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -5339,11 +5336,11 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5365,13 +5362,13 @@
         <v>127</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M32" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
@@ -5412,7 +5409,7 @@
         <v>130</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>73</v>
@@ -5421,7 +5418,7 @@
         <v>131</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>74</v>
@@ -5439,7 +5436,7 @@
         <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5479,16 +5476,16 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>73</v>
@@ -5537,7 +5534,7 @@
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5555,21 +5552,21 @@
         <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5592,16 +5589,16 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
@@ -5651,7 +5648,7 @@
         <v>73</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>74</v>
@@ -5669,21 +5666,21 @@
         <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5709,14 +5706,14 @@
         <v>102</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>73</v>
@@ -5765,7 +5762,7 @@
         <v>73</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>74</v>
@@ -5783,21 +5780,21 @@
         <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5820,17 +5817,17 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>73</v>
@@ -5879,7 +5876,7 @@
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
@@ -5897,21 +5894,21 @@
         <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5934,19 +5931,19 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="K37" t="s" s="2">
+      <c r="L37" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>73</v>
@@ -5995,7 +5992,7 @@
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -6013,21 +6010,21 @@
         <v>73</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6050,19 +6047,19 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>73</v>
@@ -6111,7 +6108,7 @@
         <v>73</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
@@ -6129,21 +6126,21 @@
         <v>73</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6166,13 +6163,13 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -6202,11 +6199,11 @@
         <v>106</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y39" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
       </c>
@@ -6223,7 +6220,7 @@
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>74</v>
@@ -6238,24 +6235,24 @@
         <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AK39" t="s" s="2">
+      <c r="AL39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6278,13 +6275,13 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="K40" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="K40" t="s" s="2">
+      <c r="L40" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6335,7 +6332,7 @@
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
@@ -6350,10 +6347,10 @@
         <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6367,7 +6364,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6390,16 +6387,16 @@
         <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="K41" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="K41" t="s" s="2">
+      <c r="L41" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
@@ -6449,7 +6446,7 @@
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>74</v>
@@ -6464,24 +6461,24 @@
         <v>94</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6504,13 +6501,13 @@
         <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -6561,7 +6558,7 @@
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
@@ -6579,21 +6576,21 @@
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6616,13 +6613,13 @@
         <v>73</v>
       </c>
       <c r="J43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="K43" t="s" s="2">
+      <c r="L43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -6673,7 +6670,7 @@
         <v>73</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>74</v>
@@ -6688,16 +6685,16 @@
         <v>94</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AK43" t="s" s="2">
+      <c r="AL43" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>73</v>
@@ -6705,7 +6702,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6728,13 +6725,13 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="K44" t="s" s="2">
+      <c r="L44" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6785,7 +6782,7 @@
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>74</v>
@@ -6800,24 +6797,24 @@
         <v>94</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AK44" t="s" s="2">
+      <c r="AL44" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6840,13 +6837,13 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6897,7 +6894,7 @@
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
@@ -6912,24 +6909,24 @@
         <v>94</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>374</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6952,13 +6949,13 @@
         <v>73</v>
       </c>
       <c r="J46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="K46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="K46" t="s" s="2">
+      <c r="L46" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7009,7 +7006,7 @@
         <v>73</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>74</v>
@@ -7024,13 +7021,13 @@
         <v>94</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>73</v>
@@ -7041,7 +7038,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7064,13 +7061,13 @@
         <v>73</v>
       </c>
       <c r="J47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="K47" t="s" s="2">
+      <c r="L47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7121,7 +7118,7 @@
         <v>73</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
@@ -7139,7 +7136,7 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -7153,7 +7150,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7176,16 +7173,16 @@
         <v>73</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
@@ -7235,7 +7232,7 @@
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>74</v>
@@ -7250,13 +7247,13 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>73</v>
@@ -7267,7 +7264,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7290,16 +7287,16 @@
         <v>73</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
@@ -7349,7 +7346,7 @@
         <v>73</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>74</v>
@@ -7364,24 +7361,24 @@
         <v>94</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AK49" t="s" s="2">
+      <c r="AL49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AM49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7404,13 +7401,13 @@
         <v>73</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -7461,7 +7458,7 @@
         <v>73</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>74</v>
@@ -7479,25 +7476,25 @@
         <v>73</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7516,13 +7513,13 @@
         <v>73</v>
       </c>
       <c r="J51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="K51" t="s" s="2">
+      <c r="L51" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7573,7 +7570,7 @@
         <v>73</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>74</v>
@@ -7588,10 +7585,10 @@
         <v>94</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7605,7 +7602,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7628,13 +7625,13 @@
         <v>73</v>
       </c>
       <c r="J52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="K52" t="s" s="2">
+      <c r="L52" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -7685,7 +7682,7 @@
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>82</v>
@@ -7697,27 +7694,27 @@
         <v>73</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AJ52" t="s" s="2">
+      <c r="AK52" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7740,13 +7737,13 @@
         <v>73</v>
       </c>
       <c r="J53" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K53" t="s" s="2">
+      <c r="L53" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -7797,7 +7794,7 @@
         <v>73</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>74</v>
@@ -7815,7 +7812,7 @@
         <v>73</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>73</v>
@@ -7829,11 +7826,11 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7855,13 +7852,13 @@
         <v>127</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L54" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M54" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -7911,7 +7908,7 @@
         <v>73</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>74</v>
@@ -7929,7 +7926,7 @@
         <v>73</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7943,11 +7940,11 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7969,16 +7966,16 @@
         <v>127</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="M55" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>73</v>
@@ -8027,7 +8024,7 @@
         <v>73</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>74</v>
@@ -8059,7 +8056,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8082,16 +8079,16 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8117,14 +8114,14 @@
         <v>73</v>
       </c>
       <c r="W56" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Y56" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Y56" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="Z56" t="s" s="2">
         <v>73</v>
       </c>
@@ -8141,7 +8138,7 @@
         <v>73</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>74</v>
@@ -8159,21 +8156,21 @@
         <v>73</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8196,13 +8193,13 @@
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="K57" t="s" s="2">
+      <c r="L57" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8253,7 +8250,7 @@
         <v>73</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>74</v>
@@ -8271,21 +8268,21 @@
         <v>73</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8311,10 +8308,10 @@
         <v>102</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -8341,14 +8338,14 @@
         <v>73</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Y58" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="Z58" t="s" s="2">
         <v>73</v>
       </c>
@@ -8365,7 +8362,7 @@
         <v>73</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>74</v>
@@ -8383,10 +8380,10 @@
         <v>73</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>73</v>
@@ -8397,7 +8394,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8423,10 +8420,10 @@
         <v>102</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8453,14 +8450,14 @@
         <v>73</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="Y59" t="s" s="2">
-        <v>455</v>
-      </c>
       <c r="Z59" t="s" s="2">
         <v>73</v>
       </c>
@@ -8477,7 +8474,7 @@
         <v>73</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>82</v>
@@ -8495,21 +8492,21 @@
         <v>73</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8532,13 +8529,13 @@
         <v>73</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8589,7 +8586,7 @@
         <v>73</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>74</v>
@@ -8607,7 +8604,7 @@
         <v>73</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>73</v>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8644,16 +8641,16 @@
         <v>73</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
@@ -8703,7 +8700,7 @@
         <v>73</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>74</v>
@@ -8718,19 +8715,19 @@
         <v>94</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1372,7 +1372,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>
@@ -7613,7 +7613,7 @@
         <v>82</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6812,7 +6812,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>367</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
@@ -7148,7 +7148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>385</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-AppointmentLE.xlsx
+++ b/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
